--- a/Table_diabetes_metadata.xlsx
+++ b/Table_diabetes_metadata.xlsx
@@ -417,11 +417,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Patient</t>
-        </is>
-      </c>
       <c r="B1" t="inlineStr">
         <is>
           <t>Age</t>
@@ -436,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Patient_1</t>
+          <t>Patient_ID_000</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -451,7 +446,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Patient_2</t>
+          <t>Patient_ID_001</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -466,7 +461,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Patient_3</t>
+          <t>Patient_ID_002</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -481,7 +476,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Patient_4</t>
+          <t>Patient_ID_003</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -496,7 +491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Patient_5</t>
+          <t>Patient_ID_004</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -511,7 +506,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Patient_6</t>
+          <t>Patient_ID_005</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -526,7 +521,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Patient_7</t>
+          <t>Patient_ID_006</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -541,7 +536,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Patient_8</t>
+          <t>Patient_ID_007</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -556,7 +551,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Patient_9</t>
+          <t>Patient_ID_008</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -571,7 +566,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Patient_10</t>
+          <t>Patient_ID_009</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -586,7 +581,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Patient_11</t>
+          <t>Patient_ID_010</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -601,7 +596,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Patient_12</t>
+          <t>Patient_ID_011</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -616,7 +611,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Patient_13</t>
+          <t>Patient_ID_012</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -631,7 +626,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Patient_14</t>
+          <t>Patient_ID_013</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -646,7 +641,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Patient_15</t>
+          <t>Patient_ID_014</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -661,7 +656,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Patient_16</t>
+          <t>Patient_ID_015</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -676,7 +671,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Patient_17</t>
+          <t>Patient_ID_016</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -691,7 +686,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Patient_18</t>
+          <t>Patient_ID_017</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -706,7 +701,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Patient_19</t>
+          <t>Patient_ID_018</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -721,7 +716,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Patient_20</t>
+          <t>Patient_ID_019</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -736,7 +731,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Patient_21</t>
+          <t>Patient_ID_020</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -751,7 +746,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Patient_22</t>
+          <t>Patient_ID_021</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -766,7 +761,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Patient_23</t>
+          <t>Patient_ID_022</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -781,7 +776,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Patient_24</t>
+          <t>Patient_ID_023</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -796,7 +791,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Patient_25</t>
+          <t>Patient_ID_024</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -811,7 +806,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Patient_26</t>
+          <t>Patient_ID_025</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -826,7 +821,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Patient_27</t>
+          <t>Patient_ID_026</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -841,7 +836,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Patient_28</t>
+          <t>Patient_ID_027</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -856,7 +851,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Patient_29</t>
+          <t>Patient_ID_028</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -871,7 +866,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Patient_30</t>
+          <t>Patient_ID_029</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -886,7 +881,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Patient_31</t>
+          <t>Patient_ID_030</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -901,7 +896,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Patient_32</t>
+          <t>Patient_ID_031</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -916,7 +911,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Patient_33</t>
+          <t>Patient_ID_032</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -931,7 +926,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Patient_34</t>
+          <t>Patient_ID_033</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -946,7 +941,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Patient_35</t>
+          <t>Patient_ID_034</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -961,7 +956,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Patient_36</t>
+          <t>Patient_ID_035</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -976,7 +971,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Patient_37</t>
+          <t>Patient_ID_036</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -991,7 +986,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Patient_38</t>
+          <t>Patient_ID_037</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1006,7 +1001,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Patient_39</t>
+          <t>Patient_ID_038</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1021,7 +1016,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Patient_40</t>
+          <t>Patient_ID_039</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1036,7 +1031,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Patient_41</t>
+          <t>Patient_ID_040</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1051,7 +1046,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Patient_42</t>
+          <t>Patient_ID_041</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1066,7 +1061,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Patient_43</t>
+          <t>Patient_ID_042</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1081,7 +1076,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Patient_44</t>
+          <t>Patient_ID_043</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1096,7 +1091,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Patient_45</t>
+          <t>Patient_ID_044</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1111,7 +1106,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Patient_46</t>
+          <t>Patient_ID_045</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1126,7 +1121,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Patient_47</t>
+          <t>Patient_ID_046</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1141,7 +1136,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Patient_48</t>
+          <t>Patient_ID_047</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1156,7 +1151,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Patient_49</t>
+          <t>Patient_ID_048</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1171,7 +1166,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Patient_50</t>
+          <t>Patient_ID_049</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1186,7 +1181,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Patient_51</t>
+          <t>Patient_ID_050</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1201,7 +1196,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Patient_52</t>
+          <t>Patient_ID_051</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1216,7 +1211,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Patient_53</t>
+          <t>Patient_ID_052</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1231,7 +1226,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Patient_54</t>
+          <t>Patient_ID_053</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1246,7 +1241,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Patient_55</t>
+          <t>Patient_ID_054</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1261,7 +1256,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Patient_56</t>
+          <t>Patient_ID_055</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1276,7 +1271,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Patient_57</t>
+          <t>Patient_ID_056</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1291,7 +1286,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Patient_58</t>
+          <t>Patient_ID_057</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1306,7 +1301,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Patient_59</t>
+          <t>Patient_ID_058</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1321,7 +1316,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Patient_60</t>
+          <t>Patient_ID_059</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1336,7 +1331,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Patient_61</t>
+          <t>Patient_ID_060</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1351,7 +1346,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Patient_62</t>
+          <t>Patient_ID_061</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1366,7 +1361,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Patient_63</t>
+          <t>Patient_ID_062</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1381,7 +1376,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Patient_64</t>
+          <t>Patient_ID_063</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1396,7 +1391,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Patient_65</t>
+          <t>Patient_ID_064</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1411,7 +1406,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Patient_66</t>
+          <t>Patient_ID_065</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1426,7 +1421,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Patient_67</t>
+          <t>Patient_ID_066</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1441,7 +1436,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Patient_68</t>
+          <t>Patient_ID_067</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1456,7 +1451,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Patient_69</t>
+          <t>Patient_ID_068</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1471,7 +1466,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Patient_70</t>
+          <t>Patient_ID_069</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1486,7 +1481,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Patient_71</t>
+          <t>Patient_ID_070</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1501,7 +1496,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Patient_72</t>
+          <t>Patient_ID_071</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1516,7 +1511,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Patient_73</t>
+          <t>Patient_ID_072</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1531,7 +1526,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Patient_74</t>
+          <t>Patient_ID_073</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1546,7 +1541,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Patient_75</t>
+          <t>Patient_ID_074</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1561,7 +1556,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Patient_76</t>
+          <t>Patient_ID_075</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1576,7 +1571,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Patient_77</t>
+          <t>Patient_ID_076</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1591,7 +1586,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Patient_78</t>
+          <t>Patient_ID_077</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1606,7 +1601,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Patient_79</t>
+          <t>Patient_ID_078</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1621,7 +1616,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Patient_80</t>
+          <t>Patient_ID_079</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1636,7 +1631,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Patient_81</t>
+          <t>Patient_ID_080</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1651,7 +1646,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Patient_82</t>
+          <t>Patient_ID_081</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1666,7 +1661,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Patient_83</t>
+          <t>Patient_ID_082</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1681,7 +1676,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Patient_84</t>
+          <t>Patient_ID_083</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1696,7 +1691,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Patient_85</t>
+          <t>Patient_ID_084</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1711,7 +1706,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Patient_86</t>
+          <t>Patient_ID_085</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1726,7 +1721,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Patient_87</t>
+          <t>Patient_ID_086</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1741,7 +1736,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Patient_88</t>
+          <t>Patient_ID_087</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1756,7 +1751,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Patient_89</t>
+          <t>Patient_ID_088</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1771,7 +1766,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Patient_90</t>
+          <t>Patient_ID_089</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1786,7 +1781,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Patient_91</t>
+          <t>Patient_ID_090</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1801,7 +1796,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Patient_92</t>
+          <t>Patient_ID_091</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1816,7 +1811,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Patient_93</t>
+          <t>Patient_ID_092</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1831,7 +1826,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Patient_94</t>
+          <t>Patient_ID_093</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1846,7 +1841,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Patient_95</t>
+          <t>Patient_ID_094</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1861,7 +1856,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Patient_96</t>
+          <t>Patient_ID_095</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1876,7 +1871,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Patient_97</t>
+          <t>Patient_ID_096</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1891,7 +1886,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Patient_98</t>
+          <t>Patient_ID_097</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1906,7 +1901,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Patient_99</t>
+          <t>Patient_ID_098</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1921,7 +1916,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Patient_100</t>
+          <t>Patient_ID_099</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1936,7 +1931,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Patient_101</t>
+          <t>Patient_ID_100</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1951,7 +1946,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Patient_102</t>
+          <t>Patient_ID_101</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1966,7 +1961,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Patient_103</t>
+          <t>Patient_ID_102</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1981,7 +1976,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Patient_104</t>
+          <t>Patient_ID_103</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -1996,7 +1991,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Patient_105</t>
+          <t>Patient_ID_104</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2011,7 +2006,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Patient_106</t>
+          <t>Patient_ID_105</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2026,7 +2021,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Patient_107</t>
+          <t>Patient_ID_106</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2041,7 +2036,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Patient_108</t>
+          <t>Patient_ID_107</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2056,7 +2051,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Patient_109</t>
+          <t>Patient_ID_108</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2071,7 +2066,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Patient_110</t>
+          <t>Patient_ID_109</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2086,7 +2081,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Patient_111</t>
+          <t>Patient_ID_110</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2101,7 +2096,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Patient_112</t>
+          <t>Patient_ID_111</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2116,7 +2111,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Patient_113</t>
+          <t>Patient_ID_112</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2131,7 +2126,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Patient_114</t>
+          <t>Patient_ID_113</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2146,7 +2141,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Patient_115</t>
+          <t>Patient_ID_114</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2161,7 +2156,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Patient_116</t>
+          <t>Patient_ID_115</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2176,7 +2171,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Patient_117</t>
+          <t>Patient_ID_116</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2191,7 +2186,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Patient_118</t>
+          <t>Patient_ID_117</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2206,7 +2201,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Patient_119</t>
+          <t>Patient_ID_118</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2221,7 +2216,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Patient_120</t>
+          <t>Patient_ID_119</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2236,7 +2231,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Patient_121</t>
+          <t>Patient_ID_120</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2251,7 +2246,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Patient_122</t>
+          <t>Patient_ID_121</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2266,7 +2261,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Patient_123</t>
+          <t>Patient_ID_122</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2281,7 +2276,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Patient_124</t>
+          <t>Patient_ID_123</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2296,7 +2291,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Patient_125</t>
+          <t>Patient_ID_124</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2311,7 +2306,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Patient_126</t>
+          <t>Patient_ID_125</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2326,7 +2321,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Patient_127</t>
+          <t>Patient_ID_126</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2341,7 +2336,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Patient_128</t>
+          <t>Patient_ID_127</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2356,7 +2351,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Patient_129</t>
+          <t>Patient_ID_128</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -2371,7 +2366,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Patient_130</t>
+          <t>Patient_ID_129</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2386,7 +2381,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Patient_131</t>
+          <t>Patient_ID_130</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2401,7 +2396,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Patient_132</t>
+          <t>Patient_ID_131</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -2416,7 +2411,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Patient_133</t>
+          <t>Patient_ID_132</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -2431,7 +2426,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Patient_134</t>
+          <t>Patient_ID_133</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -2446,7 +2441,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Patient_135</t>
+          <t>Patient_ID_134</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -2461,7 +2456,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Patient_136</t>
+          <t>Patient_ID_135</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2476,7 +2471,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Patient_137</t>
+          <t>Patient_ID_136</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -2491,7 +2486,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Patient_138</t>
+          <t>Patient_ID_137</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -2506,7 +2501,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Patient_139</t>
+          <t>Patient_ID_138</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -2521,7 +2516,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Patient_140</t>
+          <t>Patient_ID_139</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -2536,7 +2531,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Patient_141</t>
+          <t>Patient_ID_140</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -2551,7 +2546,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Patient_142</t>
+          <t>Patient_ID_141</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -2566,7 +2561,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Patient_143</t>
+          <t>Patient_ID_142</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -2581,7 +2576,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Patient_144</t>
+          <t>Patient_ID_143</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -2596,7 +2591,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Patient_145</t>
+          <t>Patient_ID_144</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -2611,7 +2606,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Patient_146</t>
+          <t>Patient_ID_145</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -2626,7 +2621,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Patient_147</t>
+          <t>Patient_ID_146</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -2641,7 +2636,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Patient_148</t>
+          <t>Patient_ID_147</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -2656,7 +2651,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Patient_149</t>
+          <t>Patient_ID_148</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -2671,7 +2666,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Patient_150</t>
+          <t>Patient_ID_149</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -2686,7 +2681,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Patient_151</t>
+          <t>Patient_ID_150</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -2701,7 +2696,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Patient_152</t>
+          <t>Patient_ID_151</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -2716,7 +2711,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Patient_153</t>
+          <t>Patient_ID_152</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -2731,7 +2726,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Patient_154</t>
+          <t>Patient_ID_153</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -2746,7 +2741,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Patient_155</t>
+          <t>Patient_ID_154</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -2761,7 +2756,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Patient_156</t>
+          <t>Patient_ID_155</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -2776,7 +2771,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Patient_157</t>
+          <t>Patient_ID_156</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -2791,7 +2786,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Patient_158</t>
+          <t>Patient_ID_157</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -2806,7 +2801,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Patient_159</t>
+          <t>Patient_ID_158</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -2821,7 +2816,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Patient_160</t>
+          <t>Patient_ID_159</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -2836,7 +2831,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Patient_161</t>
+          <t>Patient_ID_160</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -2851,7 +2846,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Patient_162</t>
+          <t>Patient_ID_161</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -2866,7 +2861,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Patient_163</t>
+          <t>Patient_ID_162</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -2881,7 +2876,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Patient_164</t>
+          <t>Patient_ID_163</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -2896,7 +2891,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Patient_165</t>
+          <t>Patient_ID_164</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -2911,7 +2906,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Patient_166</t>
+          <t>Patient_ID_165</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -2926,7 +2921,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Patient_167</t>
+          <t>Patient_ID_166</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -2941,7 +2936,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Patient_168</t>
+          <t>Patient_ID_167</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -2956,7 +2951,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Patient_169</t>
+          <t>Patient_ID_168</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -2971,7 +2966,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Patient_170</t>
+          <t>Patient_ID_169</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -2986,7 +2981,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Patient_171</t>
+          <t>Patient_ID_170</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3001,7 +2996,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Patient_172</t>
+          <t>Patient_ID_171</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -3016,7 +3011,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Patient_173</t>
+          <t>Patient_ID_172</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -3031,7 +3026,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Patient_174</t>
+          <t>Patient_ID_173</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3046,7 +3041,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Patient_175</t>
+          <t>Patient_ID_174</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -3061,7 +3056,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Patient_176</t>
+          <t>Patient_ID_175</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -3076,7 +3071,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Patient_177</t>
+          <t>Patient_ID_176</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -3091,7 +3086,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Patient_178</t>
+          <t>Patient_ID_177</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -3106,7 +3101,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Patient_179</t>
+          <t>Patient_ID_178</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -3121,7 +3116,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Patient_180</t>
+          <t>Patient_ID_179</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3136,7 +3131,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Patient_181</t>
+          <t>Patient_ID_180</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3151,7 +3146,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Patient_182</t>
+          <t>Patient_ID_181</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3166,7 +3161,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Patient_183</t>
+          <t>Patient_ID_182</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -3181,7 +3176,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Patient_184</t>
+          <t>Patient_ID_183</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -3196,7 +3191,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Patient_185</t>
+          <t>Patient_ID_184</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3211,7 +3206,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Patient_186</t>
+          <t>Patient_ID_185</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3226,7 +3221,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Patient_187</t>
+          <t>Patient_ID_186</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -3241,7 +3236,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Patient_188</t>
+          <t>Patient_ID_187</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -3256,7 +3251,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Patient_189</t>
+          <t>Patient_ID_188</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3271,7 +3266,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Patient_190</t>
+          <t>Patient_ID_189</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3286,7 +3281,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Patient_191</t>
+          <t>Patient_ID_190</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3301,7 +3296,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Patient_192</t>
+          <t>Patient_ID_191</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -3316,7 +3311,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Patient_193</t>
+          <t>Patient_ID_192</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -3331,7 +3326,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Patient_194</t>
+          <t>Patient_ID_193</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -3346,7 +3341,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Patient_195</t>
+          <t>Patient_ID_194</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -3361,7 +3356,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Patient_196</t>
+          <t>Patient_ID_195</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -3376,7 +3371,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Patient_197</t>
+          <t>Patient_ID_196</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -3391,7 +3386,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Patient_198</t>
+          <t>Patient_ID_197</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -3406,7 +3401,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Patient_199</t>
+          <t>Patient_ID_198</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -3421,7 +3416,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Patient_200</t>
+          <t>Patient_ID_199</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -3436,7 +3431,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Patient_201</t>
+          <t>Patient_ID_200</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -3451,7 +3446,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Patient_202</t>
+          <t>Patient_ID_201</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -3466,7 +3461,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Patient_203</t>
+          <t>Patient_ID_202</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -3481,7 +3476,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Patient_204</t>
+          <t>Patient_ID_203</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -3496,7 +3491,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Patient_205</t>
+          <t>Patient_ID_204</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -3511,7 +3506,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Patient_206</t>
+          <t>Patient_ID_205</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -3526,7 +3521,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Patient_207</t>
+          <t>Patient_ID_206</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -3541,7 +3536,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Patient_208</t>
+          <t>Patient_ID_207</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -3556,7 +3551,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Patient_209</t>
+          <t>Patient_ID_208</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -3571,7 +3566,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Patient_210</t>
+          <t>Patient_ID_209</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -3586,7 +3581,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Patient_211</t>
+          <t>Patient_ID_210</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -3601,7 +3596,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Patient_212</t>
+          <t>Patient_ID_211</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -3616,7 +3611,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Patient_213</t>
+          <t>Patient_ID_212</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -3631,7 +3626,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Patient_214</t>
+          <t>Patient_ID_213</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -3646,7 +3641,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Patient_215</t>
+          <t>Patient_ID_214</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -3661,7 +3656,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Patient_216</t>
+          <t>Patient_ID_215</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -3676,7 +3671,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Patient_217</t>
+          <t>Patient_ID_216</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -3691,7 +3686,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Patient_218</t>
+          <t>Patient_ID_217</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -3706,7 +3701,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Patient_219</t>
+          <t>Patient_ID_218</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -3721,7 +3716,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Patient_220</t>
+          <t>Patient_ID_219</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -3736,7 +3731,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Patient_221</t>
+          <t>Patient_ID_220</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -3751,7 +3746,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Patient_222</t>
+          <t>Patient_ID_221</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -3766,7 +3761,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Patient_223</t>
+          <t>Patient_ID_222</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -3781,7 +3776,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Patient_224</t>
+          <t>Patient_ID_223</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -3796,7 +3791,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Patient_225</t>
+          <t>Patient_ID_224</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -3811,7 +3806,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Patient_226</t>
+          <t>Patient_ID_225</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -3826,7 +3821,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Patient_227</t>
+          <t>Patient_ID_226</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -3841,7 +3836,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Patient_228</t>
+          <t>Patient_ID_227</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -3856,7 +3851,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Patient_229</t>
+          <t>Patient_ID_228</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -3871,7 +3866,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Patient_230</t>
+          <t>Patient_ID_229</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -3886,7 +3881,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Patient_231</t>
+          <t>Patient_ID_230</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -3901,7 +3896,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Patient_232</t>
+          <t>Patient_ID_231</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -3916,7 +3911,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Patient_233</t>
+          <t>Patient_ID_232</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -3931,7 +3926,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Patient_234</t>
+          <t>Patient_ID_233</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -3946,7 +3941,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Patient_235</t>
+          <t>Patient_ID_234</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -3961,7 +3956,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Patient_236</t>
+          <t>Patient_ID_235</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -3976,7 +3971,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Patient_237</t>
+          <t>Patient_ID_236</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -3991,7 +3986,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Patient_238</t>
+          <t>Patient_ID_237</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -4006,7 +4001,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Patient_239</t>
+          <t>Patient_ID_238</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -4021,7 +4016,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Patient_240</t>
+          <t>Patient_ID_239</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -4036,7 +4031,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Patient_241</t>
+          <t>Patient_ID_240</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -4051,7 +4046,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Patient_242</t>
+          <t>Patient_ID_241</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -4066,7 +4061,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Patient_243</t>
+          <t>Patient_ID_242</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -4081,7 +4076,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Patient_244</t>
+          <t>Patient_ID_243</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -4096,7 +4091,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Patient_245</t>
+          <t>Patient_ID_244</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -4111,7 +4106,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Patient_246</t>
+          <t>Patient_ID_245</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -4126,7 +4121,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Patient_247</t>
+          <t>Patient_ID_246</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -4141,7 +4136,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Patient_248</t>
+          <t>Patient_ID_247</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -4156,7 +4151,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Patient_249</t>
+          <t>Patient_ID_248</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -4171,7 +4166,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Patient_250</t>
+          <t>Patient_ID_249</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -4186,7 +4181,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Patient_251</t>
+          <t>Patient_ID_250</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -4201,7 +4196,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Patient_252</t>
+          <t>Patient_ID_251</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -4216,7 +4211,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Patient_253</t>
+          <t>Patient_ID_252</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -4231,7 +4226,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Patient_254</t>
+          <t>Patient_ID_253</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -4246,7 +4241,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Patient_255</t>
+          <t>Patient_ID_254</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -4261,7 +4256,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Patient_256</t>
+          <t>Patient_ID_255</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -4276,7 +4271,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Patient_257</t>
+          <t>Patient_ID_256</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -4291,7 +4286,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Patient_258</t>
+          <t>Patient_ID_257</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -4306,7 +4301,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Patient_259</t>
+          <t>Patient_ID_258</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -4321,7 +4316,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Patient_260</t>
+          <t>Patient_ID_259</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -4336,7 +4331,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Patient_261</t>
+          <t>Patient_ID_260</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -4351,7 +4346,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Patient_262</t>
+          <t>Patient_ID_261</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -4366,7 +4361,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Patient_263</t>
+          <t>Patient_ID_262</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -4381,7 +4376,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Patient_264</t>
+          <t>Patient_ID_263</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -4396,7 +4391,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Patient_265</t>
+          <t>Patient_ID_264</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -4411,7 +4406,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Patient_266</t>
+          <t>Patient_ID_265</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -4426,7 +4421,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Patient_267</t>
+          <t>Patient_ID_266</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -4441,7 +4436,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Patient_268</t>
+          <t>Patient_ID_267</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -4456,7 +4451,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Patient_269</t>
+          <t>Patient_ID_268</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -4471,7 +4466,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Patient_270</t>
+          <t>Patient_ID_269</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -4486,7 +4481,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Patient_271</t>
+          <t>Patient_ID_270</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -4501,7 +4496,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Patient_272</t>
+          <t>Patient_ID_271</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -4516,7 +4511,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Patient_273</t>
+          <t>Patient_ID_272</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -4531,7 +4526,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Patient_274</t>
+          <t>Patient_ID_273</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -4546,7 +4541,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Patient_275</t>
+          <t>Patient_ID_274</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -4561,7 +4556,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Patient_276</t>
+          <t>Patient_ID_275</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -4576,7 +4571,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Patient_277</t>
+          <t>Patient_ID_276</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -4591,7 +4586,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Patient_278</t>
+          <t>Patient_ID_277</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -4606,7 +4601,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Patient_279</t>
+          <t>Patient_ID_278</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -4621,7 +4616,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Patient_280</t>
+          <t>Patient_ID_279</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -4636,7 +4631,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Patient_281</t>
+          <t>Patient_ID_280</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -4651,7 +4646,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Patient_282</t>
+          <t>Patient_ID_281</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -4666,7 +4661,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Patient_283</t>
+          <t>Patient_ID_282</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -4681,7 +4676,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Patient_284</t>
+          <t>Patient_ID_283</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -4696,7 +4691,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Patient_285</t>
+          <t>Patient_ID_284</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -4711,7 +4706,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Patient_286</t>
+          <t>Patient_ID_285</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -4726,7 +4721,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Patient_287</t>
+          <t>Patient_ID_286</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -4741,7 +4736,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Patient_288</t>
+          <t>Patient_ID_287</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -4756,7 +4751,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Patient_289</t>
+          <t>Patient_ID_288</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -4771,7 +4766,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Patient_290</t>
+          <t>Patient_ID_289</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -4786,7 +4781,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Patient_291</t>
+          <t>Patient_ID_290</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -4801,7 +4796,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Patient_292</t>
+          <t>Patient_ID_291</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -4816,7 +4811,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Patient_293</t>
+          <t>Patient_ID_292</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -4831,7 +4826,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Patient_294</t>
+          <t>Patient_ID_293</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -4846,7 +4841,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Patient_295</t>
+          <t>Patient_ID_294</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -4861,7 +4856,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Patient_296</t>
+          <t>Patient_ID_295</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -4876,7 +4871,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Patient_297</t>
+          <t>Patient_ID_296</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -4891,7 +4886,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Patient_298</t>
+          <t>Patient_ID_297</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -4906,7 +4901,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Patient_299</t>
+          <t>Patient_ID_298</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -4921,7 +4916,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Patient_300</t>
+          <t>Patient_ID_299</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -4936,7 +4931,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Patient_301</t>
+          <t>Patient_ID_300</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -4951,7 +4946,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Patient_302</t>
+          <t>Patient_ID_301</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -4966,7 +4961,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Patient_303</t>
+          <t>Patient_ID_302</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -4981,7 +4976,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Patient_304</t>
+          <t>Patient_ID_303</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -4996,7 +4991,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Patient_305</t>
+          <t>Patient_ID_304</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -5011,7 +5006,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Patient_306</t>
+          <t>Patient_ID_305</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -5026,7 +5021,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Patient_307</t>
+          <t>Patient_ID_306</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -5041,7 +5036,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Patient_308</t>
+          <t>Patient_ID_307</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -5056,7 +5051,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Patient_309</t>
+          <t>Patient_ID_308</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -5071,7 +5066,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Patient_310</t>
+          <t>Patient_ID_309</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -5086,7 +5081,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Patient_311</t>
+          <t>Patient_ID_310</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -5101,7 +5096,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Patient_312</t>
+          <t>Patient_ID_311</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -5116,7 +5111,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Patient_313</t>
+          <t>Patient_ID_312</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -5131,7 +5126,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Patient_314</t>
+          <t>Patient_ID_313</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -5146,7 +5141,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Patient_315</t>
+          <t>Patient_ID_314</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -5161,7 +5156,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Patient_316</t>
+          <t>Patient_ID_315</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -5176,7 +5171,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Patient_317</t>
+          <t>Patient_ID_316</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -5191,7 +5186,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Patient_318</t>
+          <t>Patient_ID_317</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -5206,7 +5201,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Patient_319</t>
+          <t>Patient_ID_318</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -5221,7 +5216,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Patient_320</t>
+          <t>Patient_ID_319</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -5236,7 +5231,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Patient_321</t>
+          <t>Patient_ID_320</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -5251,7 +5246,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Patient_322</t>
+          <t>Patient_ID_321</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -5266,7 +5261,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Patient_323</t>
+          <t>Patient_ID_322</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -5281,7 +5276,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Patient_324</t>
+          <t>Patient_ID_323</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -5296,7 +5291,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Patient_325</t>
+          <t>Patient_ID_324</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -5311,7 +5306,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Patient_326</t>
+          <t>Patient_ID_325</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -5326,7 +5321,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Patient_327</t>
+          <t>Patient_ID_326</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -5341,7 +5336,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Patient_328</t>
+          <t>Patient_ID_327</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -5356,7 +5351,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Patient_329</t>
+          <t>Patient_ID_328</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -5371,7 +5366,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Patient_330</t>
+          <t>Patient_ID_329</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -5386,7 +5381,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Patient_331</t>
+          <t>Patient_ID_330</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -5401,7 +5396,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Patient_332</t>
+          <t>Patient_ID_331</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -5416,7 +5411,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Patient_333</t>
+          <t>Patient_ID_332</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -5431,7 +5426,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Patient_334</t>
+          <t>Patient_ID_333</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -5446,7 +5441,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Patient_335</t>
+          <t>Patient_ID_334</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -5461,7 +5456,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Patient_336</t>
+          <t>Patient_ID_335</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -5476,7 +5471,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Patient_337</t>
+          <t>Patient_ID_336</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -5491,7 +5486,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Patient_338</t>
+          <t>Patient_ID_337</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -5506,7 +5501,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Patient_339</t>
+          <t>Patient_ID_338</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -5521,7 +5516,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Patient_340</t>
+          <t>Patient_ID_339</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -5536,7 +5531,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Patient_341</t>
+          <t>Patient_ID_340</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -5551,7 +5546,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Patient_342</t>
+          <t>Patient_ID_341</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -5566,7 +5561,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Patient_343</t>
+          <t>Patient_ID_342</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -5581,7 +5576,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Patient_344</t>
+          <t>Patient_ID_343</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -5596,7 +5591,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Patient_345</t>
+          <t>Patient_ID_344</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -5611,7 +5606,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Patient_346</t>
+          <t>Patient_ID_345</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -5626,7 +5621,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Patient_347</t>
+          <t>Patient_ID_346</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -5641,7 +5636,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Patient_348</t>
+          <t>Patient_ID_347</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -5656,7 +5651,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Patient_349</t>
+          <t>Patient_ID_348</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -5671,7 +5666,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Patient_350</t>
+          <t>Patient_ID_349</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -5686,7 +5681,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Patient_351</t>
+          <t>Patient_ID_350</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -5701,7 +5696,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Patient_352</t>
+          <t>Patient_ID_351</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -5716,7 +5711,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Patient_353</t>
+          <t>Patient_ID_352</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -5731,7 +5726,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Patient_354</t>
+          <t>Patient_ID_353</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -5746,7 +5741,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Patient_355</t>
+          <t>Patient_ID_354</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -5761,7 +5756,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Patient_356</t>
+          <t>Patient_ID_355</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -5776,7 +5771,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Patient_357</t>
+          <t>Patient_ID_356</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -5791,7 +5786,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Patient_358</t>
+          <t>Patient_ID_357</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -5806,7 +5801,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Patient_359</t>
+          <t>Patient_ID_358</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -5821,7 +5816,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Patient_360</t>
+          <t>Patient_ID_359</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -5836,7 +5831,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Patient_361</t>
+          <t>Patient_ID_360</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -5851,7 +5846,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Patient_362</t>
+          <t>Patient_ID_361</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -5866,7 +5861,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Patient_363</t>
+          <t>Patient_ID_362</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -5881,7 +5876,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Patient_364</t>
+          <t>Patient_ID_363</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -5896,7 +5891,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Patient_365</t>
+          <t>Patient_ID_364</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -5911,7 +5906,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Patient_366</t>
+          <t>Patient_ID_365</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -5926,7 +5921,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Patient_367</t>
+          <t>Patient_ID_366</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -5941,7 +5936,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Patient_368</t>
+          <t>Patient_ID_367</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -5956,7 +5951,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Patient_369</t>
+          <t>Patient_ID_368</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -5971,7 +5966,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Patient_370</t>
+          <t>Patient_ID_369</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -5986,7 +5981,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Patient_371</t>
+          <t>Patient_ID_370</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -6001,7 +5996,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Patient_372</t>
+          <t>Patient_ID_371</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -6016,7 +6011,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Patient_373</t>
+          <t>Patient_ID_372</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -6031,7 +6026,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Patient_374</t>
+          <t>Patient_ID_373</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -6046,7 +6041,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Patient_375</t>
+          <t>Patient_ID_374</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -6061,7 +6056,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Patient_376</t>
+          <t>Patient_ID_375</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -6076,7 +6071,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Patient_377</t>
+          <t>Patient_ID_376</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -6091,7 +6086,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Patient_378</t>
+          <t>Patient_ID_377</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -6106,7 +6101,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Patient_379</t>
+          <t>Patient_ID_378</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -6121,7 +6116,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Patient_380</t>
+          <t>Patient_ID_379</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -6136,7 +6131,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Patient_381</t>
+          <t>Patient_ID_380</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -6151,7 +6146,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Patient_382</t>
+          <t>Patient_ID_381</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -6166,7 +6161,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Patient_383</t>
+          <t>Patient_ID_382</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -6181,7 +6176,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Patient_384</t>
+          <t>Patient_ID_383</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -6196,7 +6191,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Patient_385</t>
+          <t>Patient_ID_384</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -6211,7 +6206,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Patient_386</t>
+          <t>Patient_ID_385</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -6226,7 +6221,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Patient_387</t>
+          <t>Patient_ID_386</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -6241,7 +6236,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Patient_388</t>
+          <t>Patient_ID_387</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -6256,7 +6251,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Patient_389</t>
+          <t>Patient_ID_388</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -6271,7 +6266,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Patient_390</t>
+          <t>Patient_ID_389</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -6286,7 +6281,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Patient_391</t>
+          <t>Patient_ID_390</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -6301,7 +6296,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Patient_392</t>
+          <t>Patient_ID_391</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -6316,7 +6311,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Patient_393</t>
+          <t>Patient_ID_392</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -6331,7 +6326,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Patient_394</t>
+          <t>Patient_ID_393</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -6346,7 +6341,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Patient_395</t>
+          <t>Patient_ID_394</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -6361,7 +6356,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Patient_396</t>
+          <t>Patient_ID_395</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -6376,7 +6371,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Patient_397</t>
+          <t>Patient_ID_396</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -6391,7 +6386,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Patient_398</t>
+          <t>Patient_ID_397</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -6406,7 +6401,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Patient_399</t>
+          <t>Patient_ID_398</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -6421,7 +6416,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Patient_400</t>
+          <t>Patient_ID_399</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -6436,7 +6431,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Patient_401</t>
+          <t>Patient_ID_400</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -6451,7 +6446,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Patient_402</t>
+          <t>Patient_ID_401</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -6466,7 +6461,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Patient_403</t>
+          <t>Patient_ID_402</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -6481,7 +6476,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Patient_404</t>
+          <t>Patient_ID_403</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -6496,7 +6491,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Patient_405</t>
+          <t>Patient_ID_404</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -6511,7 +6506,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Patient_406</t>
+          <t>Patient_ID_405</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -6526,7 +6521,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Patient_407</t>
+          <t>Patient_ID_406</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -6541,7 +6536,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Patient_408</t>
+          <t>Patient_ID_407</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -6556,7 +6551,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Patient_409</t>
+          <t>Patient_ID_408</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -6571,7 +6566,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Patient_410</t>
+          <t>Patient_ID_409</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -6586,7 +6581,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Patient_411</t>
+          <t>Patient_ID_410</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -6601,7 +6596,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Patient_412</t>
+          <t>Patient_ID_411</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -6616,7 +6611,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Patient_413</t>
+          <t>Patient_ID_412</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -6631,7 +6626,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Patient_414</t>
+          <t>Patient_ID_413</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -6646,7 +6641,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Patient_415</t>
+          <t>Patient_ID_414</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -6661,7 +6656,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Patient_416</t>
+          <t>Patient_ID_415</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -6676,7 +6671,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Patient_417</t>
+          <t>Patient_ID_416</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -6691,7 +6686,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Patient_418</t>
+          <t>Patient_ID_417</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -6706,7 +6701,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Patient_419</t>
+          <t>Patient_ID_418</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -6721,7 +6716,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Patient_420</t>
+          <t>Patient_ID_419</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -6736,7 +6731,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Patient_421</t>
+          <t>Patient_ID_420</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -6751,7 +6746,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Patient_422</t>
+          <t>Patient_ID_421</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -6766,7 +6761,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Patient_423</t>
+          <t>Patient_ID_422</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -6781,7 +6776,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Patient_424</t>
+          <t>Patient_ID_423</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -6796,7 +6791,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Patient_425</t>
+          <t>Patient_ID_424</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -6811,7 +6806,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Patient_426</t>
+          <t>Patient_ID_425</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -6826,7 +6821,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Patient_427</t>
+          <t>Patient_ID_426</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -6841,7 +6836,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Patient_428</t>
+          <t>Patient_ID_427</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -6856,7 +6851,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Patient_429</t>
+          <t>Patient_ID_428</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -6871,7 +6866,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Patient_430</t>
+          <t>Patient_ID_429</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -6886,7 +6881,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Patient_431</t>
+          <t>Patient_ID_430</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -6901,7 +6896,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Patient_432</t>
+          <t>Patient_ID_431</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -6916,7 +6911,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Patient_433</t>
+          <t>Patient_ID_432</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -6931,7 +6926,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Patient_434</t>
+          <t>Patient_ID_433</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -6946,7 +6941,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Patient_435</t>
+          <t>Patient_ID_434</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -6961,7 +6956,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Patient_436</t>
+          <t>Patient_ID_435</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -6976,7 +6971,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Patient_437</t>
+          <t>Patient_ID_436</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -6991,7 +6986,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Patient_438</t>
+          <t>Patient_ID_437</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -7006,7 +7001,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Patient_439</t>
+          <t>Patient_ID_438</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -7021,7 +7016,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Patient_440</t>
+          <t>Patient_ID_439</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -7036,7 +7031,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Patient_441</t>
+          <t>Patient_ID_440</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -7051,7 +7046,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Patient_442</t>
+          <t>Patient_ID_441</t>
         </is>
       </c>
       <c r="B443" t="n">
